--- a/outputs/alternative_a_zero_shot.xlsx
+++ b/outputs/alternative_a_zero_shot.xlsx
@@ -477,7 +477,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mirtazapine saved my life, no side effects, even lost weight.</t>
+          <t>Mirtazapine helped patient manage depression and suicidal thoughts</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Son with Crohn's did very well on Asacol, reduced diarrhea.</t>
+          <t>Patient happy with Asacol treatment for Crohn's disease</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Quick reduction of symptoms</t>
+          <t>Reduced symptoms quickly</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Contrave immediately curbs cravings, leading to some early weight loss.</t>
+          <t>Patient reports positive initial results with Contrave</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient loves birth control, minimal side effects</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Patient using cream on face/arms; no reaction or issues so far.</t>
+          <t>No reaction to skin cream after 4 days</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper coil caused extreme pain, long periods; not for reviewer.</t>
+          <t>Copper coil not suitable for heavy painful periods</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Great, significantly reduced chronic headaches, minor sleepiness expected to improve.</t>
+          <t>Patient reports improvement in headaches after starting treatment</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Patient struggling with methadone withdrawal, terrified, seeks encouragement.</t>
+          <t>Methadone withdrawal, seeking encouragement to quit</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Effective birth control, but severe side effects: mood swings, dryness, acne.</t>
+          <t>Patient had mixed results with pill, experienced side effects</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brisdelle: Hot flashes subsided, but severe side effects and no support.</t>
+          <t>Patient had bad experience with Brisdelle and Noven</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Day one treatment: burns, leaks, but patient is hopeful.</t>
+          <t>Treatment works despite minor side effects</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ineffective, didn't curb appetite or feel full. A waste of money.</t>
+          <t>Product did not curb appetite, ineffective</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>No issues noted, advised dietary caution.</t>
+          <t>Patient has no issues, advises healthy eating.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ambien helped sleep under stress, but caused memory loss and rebound sleeplessness.</t>
+          <t>Rebound insomnia after Ambien discontinuation</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Provigil ineffective; Nuvigil plus Xyrem improved narcolepsy significantly, feeling great.</t>
+          <t>Provigil and Nuvigil helped patient stay awake</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Quit smoking after 50+ years; great product, six years smoke-free.</t>
+          <t>Quitted smoking after one week with great product</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>New pill caused severe acne, irregular periods, and moodiness.</t>
+          <t>Birth control caused severe acne and mood swings</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Medication helped sleep and anxiety, but lost effectiveness</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Felt 99% better after just one dose of ciprofloxacin.</t>
+          <t>Patient felt 99% better after one dose</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Patient experienced extreme wiring, no sleep improvement; least effective medication.</t>
+          <t>Patient had poor experience with sleep medication</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient happy with treatment, relieved from symptoms</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient experienced intense, unsettling effects from product</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Dry eyes not helped</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient finds oxybutynin effective for hyperhidrosis, but notes side effects</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Medication misuse in Bipolar 2 treatment</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Klonopin helped patient regain life</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Worked quickly and well. Weekly trimming is key for effectiveness.</t>
+          <t>Quick and effective nail trimming method</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Improved sleep quality, no side effects</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient reports improvement in bipolar II disorder treatment</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient loves product, sees improvement in symptoms</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient thrilled with Soolantra for rosacea, sees improvement</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1533,12 +1533,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient found prep tolerable despite initial taste issues</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Movantik causes withdrawal symptoms, may not work as expected</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1595,12 +1595,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Back and leg pain, occasional arm pain</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient unhappy with Actos side effects and dosage</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1661,12 +1661,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient finds relief from pain on lower dose</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1694,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Improved mental clarity and libido after stopping birth control</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient found medicine helped them feel happy and back to self.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Egrifta failed to reduce abdominal fat, caused irritation</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1793,12 +1793,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Overcame addiction to morphine and drinking after surgery</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gabapentin improved depression at higher dose; patient wants more.</t>
+          <t>Gabapentin improves depression and impulse control at higher doses</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Plan B taken after condom broke; period came early.</t>
+          <t>Condom broke, took Plan B, relieved after early period</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1897,12 +1897,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient had horrible side effects from Aubra birth control</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient had side effects, missed pill, and early pregnancy</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1963,12 +1963,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient finds NuvaRing effective and hassle-free alternative to oral pill</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1996,12 +1996,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient had bad side effects from microgestin replacement</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2029,12 +2029,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient finds Wellbutrin beneficial despite some side effects</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Product is effective and works for the user.</t>
+          <t>Patient says product works for them</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Medication dried out acne but caused new breakouts</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Birth control causes anxiety and depression, patient seeks removal</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2162,12 +2162,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient experiences severe burning with Monistat cream</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient experiencing side effects from antibiotic</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2228,12 +2228,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t xml:space="preserve"> Nexplanon causes emotional issues and irregular periods</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2261,12 +2261,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Improved acne, reduced depression and severity</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2294,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Flomax relieves BPH symptoms, but causes new issues</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Improved pain, but side effects persist</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2360,12 +2360,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient experienced side effects, including acne and emotional distress</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Medication worked well at first, but lost effectiveness over time</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2428,12 +2428,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient finds acne treatment effective, regains confidence</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2461,12 +2461,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient had mixed results with Mirapex/Pramepexole treatment</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Procedure was relatively painless and effective</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2527,12 +2527,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient had severe allergic reaction to product</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient had severe anxiety and withdrawal symptoms after taking medication.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient experienced rare side effects from nifedipine/Procardia</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2626,12 +2626,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient finds medication helpful for managing emotions and thoughts</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Afrezza helps manage diabetes effectively</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Zoloft worsened depression and side effects</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2725,12 +2725,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Geodon effectively eliminated auditory hallucinations</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2758,12 +2758,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient had severe allergic reaction to Bactrim</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient had skin issues and weight gain on Blisovi</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2824,12 +2824,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient found Zoloft helped them overcome depression and anxiety</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient found Drysol effective for hyperhidrosis but had side effects</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient had severe side effects from Effexor XR</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2923,12 +2923,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient had IUD removed due to severe discomfort</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2956,12 +2956,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Pregabalin reversed anxiety and improved well-being</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2990,12 +2990,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient experiences side effects, bleeding issues with new birth control</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient finds relief from pain with Ultram medication</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3056,12 +3056,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Weight loss, not hungry</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient found relief on Effexor after years of trial</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient reports positive Campral experience after rehab</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3155,12 +3155,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient had severe side effects from Effexor</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3188,12 +3188,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Got Plan B pill, relieved no pregnancy</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3221,12 +3221,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient did not like medication, prefers alternative</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3254,12 +3254,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Beneficial for extreme pain when taken with muscle relaxer.</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3287,12 +3287,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient reports positive experience with Aviane after initial fears</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3320,12 +3320,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Medication helps migraines and tremors, but insurance change hurts</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Phenergan suppository helps with migraine variant symptoms</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3386,12 +3386,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Cream causes skin irritation, but coconut oil helps alleviate</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3419,12 +3419,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient had bad experience with treatment for knee condition</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3452,12 +3452,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Implant causes irregular periods, patient considers removal</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3485,12 +3485,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Effective for motion sickness, but hard to find</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient had excellent experience with Skyla, despite initial discomfort</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3551,12 +3551,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Medication helped bipolar symptoms, but with side effects</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3584,12 +3584,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Medicine causes fluid buildup and high blood pressure issues</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3618,12 +3618,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Medication helps with PSA and psoriasis, but has side effects</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3651,12 +3651,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient had a very bad experience</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Vicodin effective but habit forming and addictive</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3719,12 +3719,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Patient finds Azo-Standard helpful for medication side effects</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3752,12 +3752,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Procedure was quick and manageable despite initial anxiety</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
